--- a/LuBan/Design/Datas/技能/__enums__.xlsx
+++ b/LuBan/Design/Datas/技能/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -108,6 +108,39 @@
   </si>
   <si>
     <t>时间</t>
+  </si>
+  <si>
+    <t>Gas.EGameEffectStackType</t>
+  </si>
+  <si>
+    <t>不堆叠</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>来源堆叠</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>目标堆叠</t>
+  </si>
+  <si>
+    <t>Gas.EGameEffectStackExpireType</t>
+  </si>
+  <si>
+    <t>RemoveSingle</t>
+  </si>
+  <si>
+    <t>删除单层</t>
+  </si>
+  <si>
+    <t>RemoveAll</t>
+  </si>
+  <si>
+    <t>删除全部</t>
   </si>
 </sst>
 </file>
@@ -292,7 +325,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,6 +341,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.15"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -645,7 +690,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -669,16 +714,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -687,99 +732,108 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -795,7 +849,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1117,192 +1171,261 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="6"/>
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="6.66666666666667" style="4" customWidth="1"/>
-    <col min="2" max="2" width="31.5555555555556" style="4" customWidth="1"/>
-    <col min="3" max="3" width="20.7777777777778" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.4444444444444" style="4" customWidth="1"/>
-    <col min="5" max="5" width="6.77777777777778" style="4" customWidth="1"/>
-    <col min="6" max="6" width="11.4444444444444" style="4" customWidth="1"/>
-    <col min="7" max="7" width="5.22222222222222" style="4" customWidth="1"/>
-    <col min="8" max="8" width="9.44444444444444" style="4" customWidth="1"/>
-    <col min="9" max="9" width="5.66666666666667" style="4" customWidth="1"/>
-    <col min="10" max="10" width="6.11111111111111" style="4" customWidth="1"/>
-    <col min="11" max="11" width="9.77777777777778" style="4" customWidth="1"/>
-    <col min="12" max="12" width="5.22222222222222" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="7.44444444444444" style="7" customWidth="1"/>
+    <col min="2" max="2" width="36.1111111111111" style="7" customWidth="1"/>
+    <col min="3" max="3" width="20.7777777777778" style="7" customWidth="1"/>
+    <col min="4" max="4" width="16.4444444444444" style="7" customWidth="1"/>
+    <col min="5" max="5" width="7.88888888888889" style="7" customWidth="1"/>
+    <col min="6" max="6" width="11.4444444444444" style="7" customWidth="1"/>
+    <col min="7" max="7" width="5.88888888888889" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.8888888888889" style="7" customWidth="1"/>
+    <col min="9" max="9" width="9.66666666666667" style="7" customWidth="1"/>
+    <col min="10" max="10" width="6.88888888888889" style="7" customWidth="1"/>
+    <col min="11" max="11" width="11.4444444444444" style="7" customWidth="1"/>
+    <col min="12" max="12" width="5.88888888888889" style="7" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="16.2" spans="1:12">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="16.2" spans="1:12">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7" t="s">
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="7"/>
+      <c r="L3" s="10"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="15" spans="1:12">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9" t="s">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9">
+      <c r="C4" s="12"/>
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9" t="s">
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9">
+      <c r="I4" s="12"/>
+      <c r="J4" s="12">
         <v>0</v>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="15" spans="1:12">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="12">
         <v>1</v>
       </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="15" spans="1:12">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9" t="s">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="12">
         <v>2</v>
       </c>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="15" spans="1:12">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="12">
         <v>3</v>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
     </row>
+    <row r="8" s="4" customFormat="1" spans="1:12">
+      <c r="B8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="4" customFormat="1" spans="1:12">
+      <c r="H9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="4" customFormat="1" spans="1:12">
+      <c r="H10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" s="5" customFormat="1" spans="1:12">
+      <c r="B11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" s="5" customFormat="1" spans="1:12">
+      <c r="H12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" s="6" customFormat="1"/>
+    <row r="14" s="6" customFormat="1"/>
+    <row r="15" s="6" customFormat="1"/>
+    <row r="16" s="6" customFormat="1"/>
+    <row r="17" s="6" customFormat="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/LuBan/Design/Datas/技能/__enums__.xlsx
+++ b/LuBan/Design/Datas/技能/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -141,6 +141,60 @@
   </si>
   <si>
     <t>删除全部</t>
+  </si>
+  <si>
+    <t>Gas.EModifierOperation</t>
+  </si>
+  <si>
+    <t>Add</t>
+  </si>
+  <si>
+    <t>加</t>
+  </si>
+  <si>
+    <t>Minus</t>
+  </si>
+  <si>
+    <t>减</t>
+  </si>
+  <si>
+    <t>Multiply</t>
+  </si>
+  <si>
+    <t>乘</t>
+  </si>
+  <si>
+    <t>Divide</t>
+  </si>
+  <si>
+    <t>除</t>
+  </si>
+  <si>
+    <t>Override</t>
+  </si>
+  <si>
+    <t>覆</t>
+  </si>
+  <si>
+    <t>Gas.EAttributeId</t>
+  </si>
+  <si>
+    <t>HpBase</t>
+  </si>
+  <si>
+    <t>基础生命</t>
+  </si>
+  <si>
+    <t>HpMult</t>
+  </si>
+  <si>
+    <t>生命加成</t>
+  </si>
+  <si>
+    <t>HpAdd</t>
+  </si>
+  <si>
+    <t>额外生命</t>
   </si>
 </sst>
 </file>
@@ -325,7 +379,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -353,6 +407,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,7 +750,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -714,16 +774,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -732,85 +792,85 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -831,7 +891,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1171,7 +1231,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="7.44444444444444" style="7" customWidth="1"/>
@@ -1400,32 +1460,153 @@
       <c r="B11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>35</v>
-      </c>
+      <c r="H11" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5"/>
       <c r="J11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" s="5" customFormat="1" spans="1:12">
       <c r="H12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" s="5" customFormat="1" spans="1:12">
+      <c r="H13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J13" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="13" s="6" customFormat="1"/>
-    <row r="14" s="6" customFormat="1"/>
-    <row r="15" s="6" customFormat="1"/>
-    <row r="16" s="6" customFormat="1"/>
-    <row r="17" s="6" customFormat="1"/>
+    <row r="14" s="4" customFormat="1" spans="1:12">
+      <c r="B14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="4" customFormat="1" spans="1:12">
+      <c r="H15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" s="4" customFormat="1" spans="1:12">
+      <c r="H16" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J16" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" s="4" customFormat="1" spans="2:10">
+      <c r="H17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" s="4" customFormat="1" spans="2:10">
+      <c r="H18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J18" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" s="4" customFormat="1" spans="2:10">
+      <c r="H19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J19" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" s="6" customFormat="1" spans="2:10">
+      <c r="B20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" s="6" customFormat="1" spans="2:10">
+      <c r="H21" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" s="6" customFormat="1" spans="2:10">
+      <c r="H22" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" s="6" customFormat="1" spans="2:10">
+      <c r="H23" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23" s="6">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/LuBan/Design/Datas/技能/__enums__.xlsx
+++ b/LuBan/Design/Datas/技能/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="134">
   <si>
     <t>##var</t>
   </si>
@@ -107,7 +107,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>时间</t>
+    <t>持续</t>
   </si>
   <si>
     <t>Gas.EGameEffectStackType</t>
@@ -195,6 +195,240 @@
   </si>
   <si>
     <t>额外生命</t>
+  </si>
+  <si>
+    <t>HpMax</t>
+  </si>
+  <si>
+    <t>最大生命</t>
+  </si>
+  <si>
+    <t>HpNow</t>
+  </si>
+  <si>
+    <t>当前生命</t>
+  </si>
+  <si>
+    <t>AtkBase</t>
+  </si>
+  <si>
+    <t>基础攻击</t>
+  </si>
+  <si>
+    <t>AtkMult</t>
+  </si>
+  <si>
+    <t>攻击加成</t>
+  </si>
+  <si>
+    <t>AtkAdd</t>
+  </si>
+  <si>
+    <t>额外攻击</t>
+  </si>
+  <si>
+    <t>AtkNow</t>
+  </si>
+  <si>
+    <t>当前攻击</t>
+  </si>
+  <si>
+    <t>FireAtkBase</t>
+  </si>
+  <si>
+    <t>基础火焰攻击</t>
+  </si>
+  <si>
+    <t>FireAtkMult</t>
+  </si>
+  <si>
+    <t>火焰攻击加成</t>
+  </si>
+  <si>
+    <t>FireAtkAdd</t>
+  </si>
+  <si>
+    <t>额外火焰攻击</t>
+  </si>
+  <si>
+    <t>FireAtkNow</t>
+  </si>
+  <si>
+    <t>当前火焰攻击</t>
+  </si>
+  <si>
+    <t>IceAtkBase</t>
+  </si>
+  <si>
+    <t>基础冰霜攻击</t>
+  </si>
+  <si>
+    <t>IceAtkMult</t>
+  </si>
+  <si>
+    <t>冰霜攻击加成</t>
+  </si>
+  <si>
+    <t>IceAtkAdd</t>
+  </si>
+  <si>
+    <t>额外冰霜攻击</t>
+  </si>
+  <si>
+    <t>IceAtkNow</t>
+  </si>
+  <si>
+    <t>当前冰霜攻击</t>
+  </si>
+  <si>
+    <t>LightAtkBase</t>
+  </si>
+  <si>
+    <t>基础闪电攻击</t>
+  </si>
+  <si>
+    <t>LightAtkMult</t>
+  </si>
+  <si>
+    <t>闪电攻击加成</t>
+  </si>
+  <si>
+    <t>LightAtkAdd</t>
+  </si>
+  <si>
+    <t>额外闪电攻击</t>
+  </si>
+  <si>
+    <t>LightAtkNow</t>
+  </si>
+  <si>
+    <t>当前闪电攻击</t>
+  </si>
+  <si>
+    <t>ChaosAtkBase</t>
+  </si>
+  <si>
+    <t>基础混乱攻击</t>
+  </si>
+  <si>
+    <t>ChaosAtkMult</t>
+  </si>
+  <si>
+    <t>混乱攻击加成</t>
+  </si>
+  <si>
+    <t>ChaosAtkAdd</t>
+  </si>
+  <si>
+    <t>额外混乱攻击</t>
+  </si>
+  <si>
+    <t>ChaosAtkNow</t>
+  </si>
+  <si>
+    <t>当前混乱攻击</t>
+  </si>
+  <si>
+    <t>ArmorBase</t>
+  </si>
+  <si>
+    <t>基础护甲</t>
+  </si>
+  <si>
+    <t>ArmorMult</t>
+  </si>
+  <si>
+    <t>护甲加成</t>
+  </si>
+  <si>
+    <t>ArmorAdd</t>
+  </si>
+  <si>
+    <t>额外护甲</t>
+  </si>
+  <si>
+    <t>ArmorNow</t>
+  </si>
+  <si>
+    <t>当前护甲</t>
+  </si>
+  <si>
+    <t>FireArmorNow</t>
+  </si>
+  <si>
+    <t>火焰抗性</t>
+  </si>
+  <si>
+    <t>FireArmorMax</t>
+  </si>
+  <si>
+    <t>最大火焰抗性</t>
+  </si>
+  <si>
+    <t>IceArmorNow</t>
+  </si>
+  <si>
+    <t>冰霜抗性</t>
+  </si>
+  <si>
+    <t>IceArmorMax</t>
+  </si>
+  <si>
+    <t>最大冰霜抗性</t>
+  </si>
+  <si>
+    <t>LightArmorNow</t>
+  </si>
+  <si>
+    <t>闪电抗性</t>
+  </si>
+  <si>
+    <t>LightArmorMax</t>
+  </si>
+  <si>
+    <t>最大闪电抗性</t>
+  </si>
+  <si>
+    <t>ChaosArmorNow</t>
+  </si>
+  <si>
+    <t>混乱抗性</t>
+  </si>
+  <si>
+    <t>ChaosArmorMax</t>
+  </si>
+  <si>
+    <t>最大混乱抗性</t>
+  </si>
+  <si>
+    <t>ShieldBase</t>
+  </si>
+  <si>
+    <t>基础护盾</t>
+  </si>
+  <si>
+    <t>ShieldMult</t>
+  </si>
+  <si>
+    <t>护盾加成</t>
+  </si>
+  <si>
+    <t>ShieldAdd</t>
+  </si>
+  <si>
+    <t>额外护盾</t>
+  </si>
+  <si>
+    <t>ShieldMax</t>
+  </si>
+  <si>
+    <t>最大护盾</t>
+  </si>
+  <si>
+    <t>ShieldNow</t>
+  </si>
+  <si>
+    <t>当前护盾</t>
   </si>
 </sst>
 </file>
@@ -207,7 +441,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,12 +452,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -379,7 +607,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -413,6 +641,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -744,137 +978,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -885,31 +1119,64 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1231,191 +1498,190 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <dimension ref="A1:L67"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="7.44444444444444" style="7" customWidth="1"/>
-    <col min="2" max="2" width="36.1111111111111" style="7" customWidth="1"/>
-    <col min="3" max="3" width="20.7777777777778" style="7" customWidth="1"/>
-    <col min="4" max="4" width="16.4444444444444" style="7" customWidth="1"/>
-    <col min="5" max="5" width="7.88888888888889" style="7" customWidth="1"/>
-    <col min="6" max="6" width="11.4444444444444" style="7" customWidth="1"/>
-    <col min="7" max="7" width="5.88888888888889" style="7" customWidth="1"/>
-    <col min="8" max="8" width="15.8888888888889" style="7" customWidth="1"/>
-    <col min="9" max="9" width="9.66666666666667" style="7" customWidth="1"/>
-    <col min="10" max="10" width="6.88888888888889" style="7" customWidth="1"/>
-    <col min="11" max="11" width="11.4444444444444" style="7" customWidth="1"/>
-    <col min="12" max="12" width="5.88888888888889" style="7" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="7.44166666666667" style="12" customWidth="1"/>
+    <col min="2" max="2" width="36.1083333333333" style="12" customWidth="1"/>
+    <col min="3" max="3" width="20.775" style="12" customWidth="1"/>
+    <col min="4" max="4" width="16.4416666666667" style="12" customWidth="1"/>
+    <col min="5" max="5" width="7.89166666666667" style="12" customWidth="1"/>
+    <col min="6" max="6" width="11.4416666666667" style="12" customWidth="1"/>
+    <col min="7" max="7" width="5.89166666666667" style="12" customWidth="1"/>
+    <col min="8" max="8" width="15.8916666666667" style="13" customWidth="1"/>
+    <col min="9" max="9" width="12.9166666666667" style="13" customWidth="1"/>
+    <col min="10" max="10" width="6.89166666666667" style="14" customWidth="1"/>
+    <col min="11" max="11" width="11.4416666666667" style="12" customWidth="1"/>
+    <col min="12" max="12" width="5.89166666666667" style="12" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.2" spans="1:12">
-      <c r="A1" s="8" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:12">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="16.2" spans="1:12">
-      <c r="A2" s="8" t="s">
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:12">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="10"/>
-    </row>
-    <row r="4" s="3" customFormat="1" ht="15" spans="1:12">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12" t="s">
+    </row>
+    <row r="4" s="3" customFormat="1" spans="1:12">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5">
         <v>1</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12">
+      <c r="I4" s="5"/>
+      <c r="J4" s="5">
         <v>0</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-    </row>
-    <row r="5" s="3" customFormat="1" ht="15" spans="1:12">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12" t="s">
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" s="3" customFormat="1" spans="1:12">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="5">
         <v>1</v>
       </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-    </row>
-    <row r="6" s="3" customFormat="1" ht="15" spans="1:12">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+    </row>
+    <row r="6" s="3" customFormat="1" spans="1:12">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="5">
         <v>2</v>
       </c>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-    </row>
-    <row r="7" s="3" customFormat="1" ht="15" spans="1:12">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12" t="s">
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" s="3" customFormat="1" spans="1:12">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="5">
         <v>3</v>
       </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
     </row>
     <row r="8" s="4" customFormat="1" spans="1:12">
       <c r="B8" s="4" t="s">
@@ -1460,7 +1726,7 @@
       <c r="B11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I11" s="5"/>
@@ -1526,7 +1792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" s="4" customFormat="1" spans="2:10">
+    <row r="17" s="4" customFormat="1" spans="1:10">
       <c r="H17" s="4" t="s">
         <v>43</v>
       </c>
@@ -1537,7 +1803,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" s="4" customFormat="1" spans="2:10">
+    <row r="18" s="4" customFormat="1" spans="1:10">
       <c r="H18" s="4" t="s">
         <v>45</v>
       </c>
@@ -1548,7 +1814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" s="4" customFormat="1" spans="2:10">
+    <row r="19" s="4" customFormat="1" spans="1:10">
       <c r="H19" s="4" t="s">
         <v>47</v>
       </c>
@@ -1559,7 +1825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" s="6" customFormat="1" spans="2:10">
+    <row r="20" s="6" customFormat="1" spans="1:10">
       <c r="B20" s="6" t="s">
         <v>49</v>
       </c>
@@ -1574,37 +1840,503 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" s="6" customFormat="1" spans="2:10">
-      <c r="H21" s="6" t="s">
+    <row r="21" s="7" customFormat="1" spans="1:10">
+      <c r="A21" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" s="6" customFormat="1" spans="1:10">
+      <c r="H22" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I22" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="J21" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" s="6" customFormat="1" spans="2:10">
-      <c r="H22" s="6" t="s">
+      <c r="J22" s="6">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" s="6" customFormat="1" spans="1:10">
+      <c r="H23" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I23" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="J22" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" s="6" customFormat="1" spans="2:10">
-      <c r="H23" s="6" t="s">
+      <c r="J23" s="6">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" s="6" customFormat="1" spans="1:10">
+      <c r="H24" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I24" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="6">
-        <v>3</v>
+      <c r="J24" s="6">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" s="8" customFormat="1" spans="1:10">
+      <c r="H25" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J25" s="6">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" s="8" customFormat="1" spans="1:10">
+      <c r="H26" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J26" s="6">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" s="9" customFormat="1" spans="1:10">
+      <c r="A27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+    </row>
+    <row r="28" s="8" customFormat="1" spans="1:10">
+      <c r="H28" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J28" s="6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="29" s="8" customFormat="1" spans="1:10">
+      <c r="H29" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J29" s="6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30" s="8" customFormat="1" spans="1:10">
+      <c r="H30" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J30" s="6">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" s="8" customFormat="1" spans="1:10">
+      <c r="H31" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J31" s="6">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="32" s="8" customFormat="1" spans="1:10">
+      <c r="H32" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J32" s="6">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="33" s="8" customFormat="1" spans="1:10">
+      <c r="H33" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J33" s="6">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="34" s="8" customFormat="1" spans="1:10">
+      <c r="H34" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="J34" s="6">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="35" s="8" customFormat="1" spans="1:10">
+      <c r="H35" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J35" s="6">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="36" s="8" customFormat="1" spans="1:10">
+      <c r="H36" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J36" s="6">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="37" s="8" customFormat="1" spans="1:10">
+      <c r="H37" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J37" s="6">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="38" s="8" customFormat="1" spans="1:10">
+      <c r="H38" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="J38" s="6">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="39" s="8" customFormat="1" spans="1:10">
+      <c r="H39" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J39" s="6">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="40" s="8" customFormat="1" spans="1:10">
+      <c r="H40" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J40" s="6">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="41" s="8" customFormat="1" spans="1:10">
+      <c r="H41" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J41" s="6">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="42" s="8" customFormat="1" spans="1:10">
+      <c r="H42" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J42" s="6">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="43" s="8" customFormat="1" spans="1:10">
+      <c r="H43" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J43" s="6">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="44" s="8" customFormat="1" spans="1:10">
+      <c r="H44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J44" s="6">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" s="8" customFormat="1" spans="1:10">
+      <c r="H45" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="J45" s="6">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="46" s="8" customFormat="1" spans="1:10">
+      <c r="H46" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J46" s="6">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="47" s="8" customFormat="1" spans="1:10">
+      <c r="H47" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="J47" s="6">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="48" s="9" customFormat="1" spans="1:10">
+      <c r="A48" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+    </row>
+    <row r="49" s="8" customFormat="1" spans="1:10">
+      <c r="H49" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="J49" s="6">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="50" s="8" customFormat="1" spans="1:10">
+      <c r="H50" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="J50" s="6">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="51" s="8" customFormat="1" spans="1:10">
+      <c r="H51" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J51" s="6">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="52" s="8" customFormat="1" spans="1:10">
+      <c r="H52" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J52" s="6">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="53" s="9" customFormat="1" spans="1:10">
+      <c r="A53" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H53" s="7"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="7"/>
+    </row>
+    <row r="54" s="8" customFormat="1" spans="1:10">
+      <c r="H54" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="J54" s="6">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="55" s="8" customFormat="1" spans="1:10">
+      <c r="H55" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="J55" s="6">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="56" s="8" customFormat="1" spans="1:10">
+      <c r="H56" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="J56" s="6">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="57" s="8" customFormat="1" spans="1:10">
+      <c r="H57" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J57" s="6">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="58" s="8" customFormat="1" spans="1:10">
+      <c r="H58" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="J58" s="6">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="59" s="8" customFormat="1" spans="1:10">
+      <c r="H59" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="J59" s="6">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="60" s="8" customFormat="1" spans="1:10">
+      <c r="H60" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="J60" s="6">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="61" s="8" customFormat="1" spans="1:10">
+      <c r="H61" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="J61" s="6">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="62" s="10" customFormat="1" spans="1:10">
+      <c r="A62" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62" s="21"/>
+      <c r="I62" s="21"/>
+      <c r="J62" s="21"/>
+    </row>
+    <row r="63" s="11" customFormat="1" spans="1:10">
+      <c r="H63" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="I63" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="J63" s="23">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="64" s="11" customFormat="1" spans="1:10">
+      <c r="H64" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="I64" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="J64" s="23">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="65" s="11" customFormat="1" spans="8:10">
+      <c r="H65" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I65" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="J65" s="23">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="66" s="11" customFormat="1" spans="8:10">
+      <c r="H66" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="I66" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="J66" s="23">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="67" s="11" customFormat="1" ht="16" customHeight="1" spans="8:10">
+      <c r="H67" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="I67" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="J67" s="23">
+        <v>505</v>
       </c>
     </row>
   </sheetData>

--- a/LuBan/Design/Datas/技能/__enums__.xlsx
+++ b/LuBan/Design/Datas/技能/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="144">
   <si>
     <t>##var</t>
   </si>
@@ -207,6 +207,36 @@
   </si>
   <si>
     <t>当前生命</t>
+  </si>
+  <si>
+    <t>MpBase</t>
+  </si>
+  <si>
+    <t>基础法力</t>
+  </si>
+  <si>
+    <t>MpMult</t>
+  </si>
+  <si>
+    <t>法力加成</t>
+  </si>
+  <si>
+    <t>MpAdd</t>
+  </si>
+  <si>
+    <t>额外法力</t>
+  </si>
+  <si>
+    <t>MpNow</t>
+  </si>
+  <si>
+    <t>最大法力</t>
+  </si>
+  <si>
+    <t>MpMax</t>
+  </si>
+  <si>
+    <t>当前法力</t>
   </si>
   <si>
     <t>AtkBase</t>
@@ -1108,7 +1138,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1137,47 +1167,23 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1498,22 +1504,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="7.44166666666667" style="12" customWidth="1"/>
-    <col min="2" max="2" width="36.1083333333333" style="12" customWidth="1"/>
-    <col min="3" max="3" width="20.775" style="12" customWidth="1"/>
-    <col min="4" max="4" width="16.4416666666667" style="12" customWidth="1"/>
-    <col min="5" max="5" width="7.89166666666667" style="12" customWidth="1"/>
-    <col min="6" max="6" width="11.4416666666667" style="12" customWidth="1"/>
-    <col min="7" max="7" width="5.89166666666667" style="12" customWidth="1"/>
-    <col min="8" max="8" width="15.8916666666667" style="13" customWidth="1"/>
-    <col min="9" max="9" width="12.9166666666667" style="13" customWidth="1"/>
-    <col min="10" max="10" width="6.89166666666667" style="14" customWidth="1"/>
-    <col min="11" max="11" width="11.4416666666667" style="12" customWidth="1"/>
-    <col min="12" max="12" width="5.89166666666667" style="12" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="12"/>
+    <col min="1" max="1" width="7.44166666666667" style="10" customWidth="1"/>
+    <col min="2" max="2" width="36.1083333333333" style="10" customWidth="1"/>
+    <col min="3" max="3" width="20.775" style="10" customWidth="1"/>
+    <col min="4" max="4" width="16.4416666666667" style="10" customWidth="1"/>
+    <col min="5" max="5" width="7.89166666666667" style="10" customWidth="1"/>
+    <col min="6" max="6" width="11.4416666666667" style="10" customWidth="1"/>
+    <col min="7" max="7" width="5.89166666666667" style="10" customWidth="1"/>
+    <col min="8" max="8" width="15.8916666666667" style="11" customWidth="1"/>
+    <col min="9" max="9" width="12.9166666666667" style="11" customWidth="1"/>
+    <col min="10" max="10" width="6.89166666666667" style="11" customWidth="1"/>
+    <col min="11" max="11" width="11.4416666666667" style="10" customWidth="1"/>
+    <col min="12" max="12" width="5.89166666666667" style="10" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:12">
@@ -1538,13 +1544,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1556,13 +1562,13 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="12" t="s">
         <v>10</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -1579,7 +1585,7 @@
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="13" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1588,13 +1594,13 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="19" t="s">
+      <c r="J3" s="14" t="s">
         <v>17</v>
       </c>
       <c r="K3" s="2" t="s">
@@ -1841,7 +1847,7 @@
       </c>
     </row>
     <row r="21" s="7" customFormat="1" spans="1:10">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="15" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1963,178 +1969,178 @@
         <v>205</v>
       </c>
     </row>
-    <row r="33" s="8" customFormat="1" spans="1:10">
-      <c r="H33" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="J33" s="6">
-        <v>206</v>
-      </c>
+    <row r="33" s="9" customFormat="1" spans="1:10">
+      <c r="A33" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
     </row>
     <row r="34" s="8" customFormat="1" spans="1:10">
       <c r="H34" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J34" s="6">
-        <v>207</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" s="8" customFormat="1" spans="1:10">
       <c r="H35" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J35" s="6">
-        <v>208</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" s="8" customFormat="1" spans="1:10">
       <c r="H36" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J36" s="6">
-        <v>209</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" s="8" customFormat="1" spans="1:10">
       <c r="H37" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J37" s="6">
-        <v>210</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" s="8" customFormat="1" spans="1:10">
       <c r="H38" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J38" s="6">
-        <v>211</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" s="8" customFormat="1" spans="1:10">
       <c r="H39" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J39" s="6">
-        <v>212</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" s="8" customFormat="1" spans="1:10">
       <c r="H40" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J40" s="6">
-        <v>213</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" s="8" customFormat="1" spans="1:10">
       <c r="H41" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J41" s="6">
-        <v>214</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" s="8" customFormat="1" spans="1:10">
       <c r="H42" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J42" s="6">
-        <v>215</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" s="8" customFormat="1" spans="1:10">
       <c r="H43" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J43" s="6">
-        <v>216</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" s="8" customFormat="1" spans="1:10">
       <c r="H44" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J44" s="6">
-        <v>217</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" s="8" customFormat="1" spans="1:10">
       <c r="H45" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J45" s="6">
-        <v>218</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" s="8" customFormat="1" spans="1:10">
       <c r="H46" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J46" s="6">
-        <v>219</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" s="8" customFormat="1" spans="1:10">
       <c r="H47" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J47" s="6">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="48" s="8" customFormat="1" spans="1:10">
+      <c r="H48" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="I47" s="6" t="s">
+      <c r="I48" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J47" s="6">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="48" s="9" customFormat="1" spans="1:10">
-      <c r="A48" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
+      <c r="J48" s="6">
+        <v>315</v>
+      </c>
     </row>
     <row r="49" s="8" customFormat="1" spans="1:10">
       <c r="H49" s="6" t="s">
@@ -2144,7 +2150,7 @@
         <v>101</v>
       </c>
       <c r="J49" s="6">
-        <v>301</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" s="8" customFormat="1" spans="1:10">
@@ -2155,7 +2161,7 @@
         <v>103</v>
       </c>
       <c r="J50" s="6">
-        <v>302</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" s="8" customFormat="1" spans="1:10">
@@ -2166,7 +2172,7 @@
         <v>105</v>
       </c>
       <c r="J51" s="6">
-        <v>303</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" s="8" customFormat="1" spans="1:10">
@@ -2177,27 +2183,27 @@
         <v>107</v>
       </c>
       <c r="J52" s="6">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="53" s="9" customFormat="1" spans="1:10">
-      <c r="A53" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="53" s="8" customFormat="1" spans="1:10">
+      <c r="H53" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="J53" s="6">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="54" s="9" customFormat="1" spans="1:10">
+      <c r="A54" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
-    </row>
-    <row r="54" s="8" customFormat="1" spans="1:10">
-      <c r="H54" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="J54" s="6">
-        <v>401</v>
-      </c>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
     </row>
     <row r="55" s="8" customFormat="1" spans="1:10">
       <c r="H55" s="6" t="s">
@@ -2207,7 +2213,7 @@
         <v>111</v>
       </c>
       <c r="J55" s="6">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="56" s="8" customFormat="1" spans="1:10">
@@ -2218,7 +2224,7 @@
         <v>113</v>
       </c>
       <c r="J56" s="6">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="57" s="8" customFormat="1" spans="1:10">
@@ -2229,7 +2235,7 @@
         <v>115</v>
       </c>
       <c r="J57" s="6">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="58" s="8" customFormat="1" spans="1:10">
@@ -2240,103 +2246,166 @@
         <v>117</v>
       </c>
       <c r="J58" s="6">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="59" s="8" customFormat="1" spans="1:10">
-      <c r="H59" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="J59" s="6">
-        <v>406</v>
-      </c>
+        <v>404</v>
+      </c>
+    </row>
+    <row r="59" s="9" customFormat="1" spans="1:10">
+      <c r="A59" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
     </row>
     <row r="60" s="8" customFormat="1" spans="1:10">
       <c r="H60" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J60" s="6">
-        <v>407</v>
+        <v>501</v>
       </c>
     </row>
     <row r="61" s="8" customFormat="1" spans="1:10">
       <c r="H61" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="J61" s="6">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="62" s="8" customFormat="1" spans="1:10">
+      <c r="H62" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I61" s="6" t="s">
+      <c r="I62" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="J61" s="6">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="62" s="10" customFormat="1" spans="1:10">
-      <c r="A62" s="10" t="s">
+      <c r="J62" s="6">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="63" s="8" customFormat="1" spans="1:10">
+      <c r="H63" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="J63" s="6">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="64" s="8" customFormat="1" spans="1:10">
+      <c r="H64" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J64" s="6">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="65" s="8" customFormat="1" spans="1:10">
+      <c r="H65" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="J65" s="6">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="66" s="8" customFormat="1" spans="1:10">
+      <c r="H66" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="J66" s="6">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="67" s="8" customFormat="1" spans="1:10">
+      <c r="H67" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J67" s="6">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="68" s="9" customFormat="1" spans="1:10">
+      <c r="A68" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H62" s="21"/>
-      <c r="I62" s="21"/>
-      <c r="J62" s="21"/>
-    </row>
-    <row r="63" s="11" customFormat="1" spans="1:10">
-      <c r="H63" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="I63" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="J63" s="23">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="64" s="11" customFormat="1" spans="1:10">
-      <c r="H64" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="I64" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="J64" s="23">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="65" s="11" customFormat="1" spans="8:10">
-      <c r="H65" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="I65" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="J65" s="23">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="66" s="11" customFormat="1" spans="8:10">
-      <c r="H66" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="I66" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="J66" s="23">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="67" s="11" customFormat="1" ht="16" customHeight="1" spans="8:10">
-      <c r="H67" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="I67" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="J67" s="23">
-        <v>505</v>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="7"/>
+    </row>
+    <row r="69" s="8" customFormat="1" spans="1:10">
+      <c r="H69" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="J69" s="6">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="70" s="8" customFormat="1" spans="1:10">
+      <c r="H70" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="J70" s="6">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="71" s="8" customFormat="1" spans="1:10">
+      <c r="H71" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J71" s="6">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="72" s="8" customFormat="1" spans="1:10">
+      <c r="H72" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="J72" s="6">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="73" s="8" customFormat="1" ht="16" customHeight="1" spans="1:10">
+      <c r="H73" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="J73" s="6">
+        <v>605</v>
       </c>
     </row>
   </sheetData>

--- a/LuBan/Design/Datas/技能/__enums__.xlsx
+++ b/LuBan/Design/Datas/技能/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="151">
   <si>
     <t>##var</t>
   </si>
@@ -174,6 +174,27 @@
   </si>
   <si>
     <t>覆</t>
+  </si>
+  <si>
+    <t>Gas.ESkillStagePriority</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>优先</t>
+  </si>
+  <si>
+    <t>Force</t>
+  </si>
+  <si>
+    <t>强制</t>
   </si>
   <si>
     <t>Gas.EAttributeId</t>
@@ -1138,7 +1159,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1153,6 +1174,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1504,22 +1528,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="7.44166666666667" style="10" customWidth="1"/>
-    <col min="2" max="2" width="36.1083333333333" style="10" customWidth="1"/>
-    <col min="3" max="3" width="20.775" style="10" customWidth="1"/>
-    <col min="4" max="4" width="16.4416666666667" style="10" customWidth="1"/>
-    <col min="5" max="5" width="7.89166666666667" style="10" customWidth="1"/>
-    <col min="6" max="6" width="11.4416666666667" style="10" customWidth="1"/>
-    <col min="7" max="7" width="5.89166666666667" style="10" customWidth="1"/>
-    <col min="8" max="8" width="15.8916666666667" style="11" customWidth="1"/>
-    <col min="9" max="9" width="12.9166666666667" style="11" customWidth="1"/>
-    <col min="10" max="10" width="6.89166666666667" style="11" customWidth="1"/>
-    <col min="11" max="11" width="11.4416666666667" style="10" customWidth="1"/>
-    <col min="12" max="12" width="5.89166666666667" style="10" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="10"/>
+    <col min="1" max="1" width="7.44166666666667" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.1083333333333" style="11" customWidth="1"/>
+    <col min="3" max="3" width="20.775" style="11" customWidth="1"/>
+    <col min="4" max="4" width="16.4416666666667" style="11" customWidth="1"/>
+    <col min="5" max="5" width="7.89166666666667" style="11" customWidth="1"/>
+    <col min="6" max="6" width="11.4416666666667" style="11" customWidth="1"/>
+    <col min="7" max="7" width="5.89166666666667" style="11" customWidth="1"/>
+    <col min="8" max="8" width="15.8916666666667" style="12" customWidth="1"/>
+    <col min="9" max="9" width="12.9166666666667" style="12" customWidth="1"/>
+    <col min="10" max="10" width="6.89166666666667" style="12" customWidth="1"/>
+    <col min="11" max="11" width="11.4416666666667" style="11" customWidth="1"/>
+    <col min="12" max="12" width="5.89166666666667" style="11" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:12">
@@ -1544,13 +1568,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1562,13 +1586,13 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="13" t="s">
         <v>10</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -1585,7 +1609,7 @@
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1594,13 +1618,13 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="15" t="s">
         <v>17</v>
       </c>
       <c r="K3" s="2" t="s">
@@ -1841,570 +1865,617 @@
       <c r="H20" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I20" s="6"/>
       <c r="J20" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="21" s="7" customFormat="1" spans="1:10">
-      <c r="A21" s="15" t="s">
-        <v>11</v>
+    <row r="21" s="6" customFormat="1" spans="1:10">
+      <c r="H21" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" spans="1:10">
       <c r="H22" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J22" s="6">
-        <v>101</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" s="6" customFormat="1" spans="1:10">
       <c r="H23" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J23" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" s="7" customFormat="1" spans="1:10">
+      <c r="B24" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" s="8" customFormat="1" spans="1:10">
+      <c r="A25" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" s="7" customFormat="1" spans="1:10">
+      <c r="H26" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J26" s="7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" s="7" customFormat="1" spans="1:10">
+      <c r="H27" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J27" s="7">
         <v>102</v>
       </c>
     </row>
-    <row r="24" s="6" customFormat="1" spans="1:10">
-      <c r="H24" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J24" s="6">
+    <row r="28" s="7" customFormat="1" spans="1:10">
+      <c r="H28" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J28" s="7">
         <v>103</v>
       </c>
     </row>
-    <row r="25" s="8" customFormat="1" spans="1:10">
-      <c r="H25" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="J25" s="6">
+    <row r="29" s="9" customFormat="1" spans="1:10">
+      <c r="H29" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J29" s="7">
         <v>104</v>
       </c>
     </row>
-    <row r="26" s="8" customFormat="1" spans="1:10">
-      <c r="H26" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J26" s="6">
+    <row r="30" s="9" customFormat="1" spans="1:10">
+      <c r="H30" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J30" s="7">
         <v>105</v>
       </c>
     </row>
-    <row r="27" s="9" customFormat="1" spans="1:10">
-      <c r="A27" s="9" t="s">
+    <row r="31" s="10" customFormat="1" spans="1:10">
+      <c r="A31" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-    </row>
-    <row r="28" s="8" customFormat="1" spans="1:10">
-      <c r="H28" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J28" s="6">
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+    </row>
+    <row r="32" s="9" customFormat="1" spans="1:10">
+      <c r="H32" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J32" s="7">
         <v>201</v>
       </c>
     </row>
-    <row r="29" s="8" customFormat="1" spans="1:10">
-      <c r="H29" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J29" s="6">
+    <row r="33" s="9" customFormat="1" spans="1:10">
+      <c r="H33" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J33" s="7">
         <v>202</v>
       </c>
     </row>
-    <row r="30" s="8" customFormat="1" spans="1:10">
-      <c r="H30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="J30" s="6">
+    <row r="34" s="9" customFormat="1" spans="1:10">
+      <c r="H34" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J34" s="7">
         <v>203</v>
       </c>
     </row>
-    <row r="31" s="8" customFormat="1" spans="1:10">
-      <c r="H31" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J31" s="6">
+    <row r="35" s="9" customFormat="1" spans="1:10">
+      <c r="H35" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J35" s="7">
         <v>204</v>
       </c>
     </row>
-    <row r="32" s="8" customFormat="1" spans="1:10">
-      <c r="H32" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J32" s="6">
+    <row r="36" s="9" customFormat="1" spans="1:10">
+      <c r="H36" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J36" s="7">
         <v>205</v>
       </c>
     </row>
-    <row r="33" s="9" customFormat="1" spans="1:10">
-      <c r="A33" s="9" t="s">
+    <row r="37" s="10" customFormat="1" spans="1:10">
+      <c r="A37" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-    </row>
-    <row r="34" s="8" customFormat="1" spans="1:10">
-      <c r="H34" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="J34" s="6">
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+    </row>
+    <row r="38" s="9" customFormat="1" spans="1:10">
+      <c r="H38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="J38" s="7">
         <v>301</v>
       </c>
     </row>
-    <row r="35" s="8" customFormat="1" spans="1:10">
-      <c r="H35" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="J35" s="6">
+    <row r="39" s="9" customFormat="1" spans="1:10">
+      <c r="H39" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J39" s="7">
         <v>302</v>
       </c>
     </row>
-    <row r="36" s="8" customFormat="1" spans="1:10">
-      <c r="H36" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="J36" s="6">
+    <row r="40" s="9" customFormat="1" spans="1:10">
+      <c r="H40" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="J40" s="7">
         <v>303</v>
       </c>
     </row>
-    <row r="37" s="8" customFormat="1" spans="1:10">
-      <c r="H37" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="J37" s="6">
+    <row r="41" s="9" customFormat="1" spans="1:10">
+      <c r="H41" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J41" s="7">
         <v>304</v>
       </c>
     </row>
-    <row r="38" s="8" customFormat="1" spans="1:10">
-      <c r="H38" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="J38" s="6">
+    <row r="42" s="9" customFormat="1" spans="1:10">
+      <c r="H42" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="J42" s="7">
         <v>305</v>
       </c>
     </row>
-    <row r="39" s="8" customFormat="1" spans="1:10">
-      <c r="H39" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J39" s="6">
+    <row r="43" s="9" customFormat="1" spans="1:10">
+      <c r="H43" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J43" s="7">
         <v>306</v>
       </c>
     </row>
-    <row r="40" s="8" customFormat="1" spans="1:10">
-      <c r="H40" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="J40" s="6">
+    <row r="44" s="9" customFormat="1" spans="1:10">
+      <c r="H44" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="J44" s="7">
         <v>307</v>
       </c>
     </row>
-    <row r="41" s="8" customFormat="1" spans="1:10">
-      <c r="H41" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="J41" s="6">
+    <row r="45" s="9" customFormat="1" spans="1:10">
+      <c r="H45" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="J45" s="7">
         <v>308</v>
       </c>
     </row>
-    <row r="42" s="8" customFormat="1" spans="1:10">
-      <c r="H42" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J42" s="6">
+    <row r="46" s="9" customFormat="1" spans="1:10">
+      <c r="H46" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="J46" s="7">
         <v>309</v>
       </c>
     </row>
-    <row r="43" s="8" customFormat="1" spans="1:10">
-      <c r="H43" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J43" s="6">
+    <row r="47" s="9" customFormat="1" spans="1:10">
+      <c r="H47" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="J47" s="7">
         <v>310</v>
       </c>
     </row>
-    <row r="44" s="8" customFormat="1" spans="1:10">
-      <c r="H44" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="J44" s="6">
+    <row r="48" s="9" customFormat="1" spans="1:10">
+      <c r="H48" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="J48" s="7">
         <v>311</v>
       </c>
     </row>
-    <row r="45" s="8" customFormat="1" spans="1:10">
-      <c r="H45" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="J45" s="6">
+    <row r="49" s="9" customFormat="1" spans="1:10">
+      <c r="H49" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="J49" s="7">
         <v>312</v>
       </c>
     </row>
-    <row r="46" s="8" customFormat="1" spans="1:10">
-      <c r="H46" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="J46" s="6">
+    <row r="50" s="9" customFormat="1" spans="1:10">
+      <c r="H50" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="J50" s="7">
         <v>313</v>
       </c>
     </row>
-    <row r="47" s="8" customFormat="1" spans="1:10">
-      <c r="H47" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="J47" s="6">
+    <row r="51" s="9" customFormat="1" spans="1:10">
+      <c r="H51" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="J51" s="7">
         <v>314</v>
       </c>
     </row>
-    <row r="48" s="8" customFormat="1" spans="1:10">
-      <c r="H48" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="J48" s="6">
+    <row r="52" s="9" customFormat="1" spans="1:10">
+      <c r="H52" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="J52" s="7">
         <v>315</v>
       </c>
     </row>
-    <row r="49" s="8" customFormat="1" spans="1:10">
-      <c r="H49" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="J49" s="6">
+    <row r="53" s="9" customFormat="1" spans="1:10">
+      <c r="H53" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="J53" s="7">
         <v>316</v>
       </c>
     </row>
-    <row r="50" s="8" customFormat="1" spans="1:10">
-      <c r="H50" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="J50" s="6">
+    <row r="54" s="9" customFormat="1" spans="1:10">
+      <c r="H54" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="J54" s="7">
         <v>317</v>
       </c>
     </row>
-    <row r="51" s="8" customFormat="1" spans="1:10">
-      <c r="H51" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="J51" s="6">
+    <row r="55" s="9" customFormat="1" spans="1:10">
+      <c r="H55" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J55" s="7">
         <v>318</v>
       </c>
     </row>
-    <row r="52" s="8" customFormat="1" spans="1:10">
-      <c r="H52" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="J52" s="6">
+    <row r="56" s="9" customFormat="1" spans="1:10">
+      <c r="H56" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="J56" s="7">
         <v>319</v>
       </c>
     </row>
-    <row r="53" s="8" customFormat="1" spans="1:10">
-      <c r="H53" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="J53" s="6">
+    <row r="57" s="9" customFormat="1" spans="1:10">
+      <c r="H57" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="J57" s="7">
         <v>320</v>
       </c>
     </row>
-    <row r="54" s="9" customFormat="1" spans="1:10">
-      <c r="A54" s="9" t="s">
+    <row r="58" s="10" customFormat="1" spans="1:10">
+      <c r="A58" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-    </row>
-    <row r="55" s="8" customFormat="1" spans="1:10">
-      <c r="H55" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="J55" s="6">
+      <c r="H58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
+    </row>
+    <row r="59" s="9" customFormat="1" spans="1:10">
+      <c r="H59" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="J59" s="7">
         <v>401</v>
       </c>
     </row>
-    <row r="56" s="8" customFormat="1" spans="1:10">
-      <c r="H56" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="J56" s="6">
+    <row r="60" s="9" customFormat="1" spans="1:10">
+      <c r="H60" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="J60" s="7">
         <v>402</v>
       </c>
     </row>
-    <row r="57" s="8" customFormat="1" spans="1:10">
-      <c r="H57" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="J57" s="6">
+    <row r="61" s="9" customFormat="1" spans="1:10">
+      <c r="H61" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="J61" s="7">
         <v>403</v>
       </c>
     </row>
-    <row r="58" s="8" customFormat="1" spans="1:10">
-      <c r="H58" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="J58" s="6">
+    <row r="62" s="9" customFormat="1" spans="1:10">
+      <c r="H62" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="J62" s="7">
         <v>404</v>
       </c>
     </row>
-    <row r="59" s="9" customFormat="1" spans="1:10">
-      <c r="A59" s="9" t="s">
+    <row r="63" s="10" customFormat="1" spans="1:10">
+      <c r="A63" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="7"/>
-    </row>
-    <row r="60" s="8" customFormat="1" spans="1:10">
-      <c r="H60" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="J60" s="6">
+      <c r="H63" s="8"/>
+      <c r="I63" s="8"/>
+      <c r="J63" s="8"/>
+    </row>
+    <row r="64" s="9" customFormat="1" spans="1:10">
+      <c r="H64" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I64" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="J64" s="7">
         <v>501</v>
       </c>
     </row>
-    <row r="61" s="8" customFormat="1" spans="1:10">
-      <c r="H61" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="I61" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="J61" s="6">
+    <row r="65" s="9" customFormat="1" spans="1:10">
+      <c r="H65" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="J65" s="7">
         <v>502</v>
       </c>
     </row>
-    <row r="62" s="8" customFormat="1" spans="1:10">
-      <c r="H62" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="J62" s="6">
+    <row r="66" s="9" customFormat="1" spans="1:10">
+      <c r="H66" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="J66" s="7">
         <v>503</v>
       </c>
     </row>
-    <row r="63" s="8" customFormat="1" spans="1:10">
-      <c r="H63" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="J63" s="6">
+    <row r="67" s="9" customFormat="1" spans="1:10">
+      <c r="H67" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="J67" s="7">
         <v>504</v>
       </c>
     </row>
-    <row r="64" s="8" customFormat="1" spans="1:10">
-      <c r="H64" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="J64" s="6">
+    <row r="68" s="9" customFormat="1" spans="1:10">
+      <c r="H68" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="J68" s="7">
         <v>505</v>
       </c>
     </row>
-    <row r="65" s="8" customFormat="1" spans="1:10">
-      <c r="H65" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="J65" s="6">
+    <row r="69" s="9" customFormat="1" spans="1:10">
+      <c r="H69" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="J69" s="7">
         <v>506</v>
       </c>
     </row>
-    <row r="66" s="8" customFormat="1" spans="1:10">
-      <c r="H66" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="J66" s="6">
+    <row r="70" s="9" customFormat="1" spans="1:10">
+      <c r="H70" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I70" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="J70" s="7">
         <v>507</v>
       </c>
     </row>
-    <row r="67" s="8" customFormat="1" spans="1:10">
-      <c r="H67" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="I67" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="J67" s="6">
+    <row r="71" s="9" customFormat="1" spans="1:10">
+      <c r="H71" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="J71" s="7">
         <v>508</v>
       </c>
     </row>
-    <row r="68" s="9" customFormat="1" spans="1:10">
-      <c r="A68" s="9" t="s">
+    <row r="72" s="10" customFormat="1" spans="1:10">
+      <c r="A72" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="7"/>
-    </row>
-    <row r="69" s="8" customFormat="1" spans="1:10">
-      <c r="H69" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="I69" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="J69" s="6">
+      <c r="H72" s="8"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8"/>
+    </row>
+    <row r="73" s="9" customFormat="1" spans="1:10">
+      <c r="H73" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="J73" s="7">
         <v>601</v>
       </c>
     </row>
-    <row r="70" s="8" customFormat="1" spans="1:10">
-      <c r="H70" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="I70" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="J70" s="6">
+    <row r="74" s="9" customFormat="1" spans="1:10">
+      <c r="H74" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="I74" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="J74" s="7">
         <v>602</v>
       </c>
     </row>
-    <row r="71" s="8" customFormat="1" spans="1:10">
-      <c r="H71" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="I71" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="J71" s="6">
+    <row r="75" s="9" customFormat="1" spans="1:10">
+      <c r="H75" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="J75" s="7">
         <v>603</v>
       </c>
     </row>
-    <row r="72" s="8" customFormat="1" spans="1:10">
-      <c r="H72" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="I72" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="J72" s="6">
+    <row r="76" s="9" customFormat="1" spans="1:10">
+      <c r="H76" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I76" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="J76" s="7">
         <v>604</v>
       </c>
     </row>
-    <row r="73" s="8" customFormat="1" ht="16" customHeight="1" spans="1:10">
-      <c r="H73" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="I73" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="J73" s="6">
+    <row r="77" s="9" customFormat="1" ht="16" customHeight="1" spans="1:10">
+      <c r="H77" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I77" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="J77" s="7">
         <v>605</v>
       </c>
     </row>
